--- a/Results/Results.out/Bovines/Data/reg_out_bv_hin_coefs.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_hin_coefs.xlsx
@@ -2909,12 +2909,12 @@
       <c r="CI14"/>
       <c r="CJ14"/>
       <c r="CK14" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="CL14"/>
       <c r="CM14"/>
       <c r="CN14" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="CO14"/>
       <c r="CP14"/>
@@ -3073,12 +3073,12 @@
       <c r="CI15"/>
       <c r="CJ15"/>
       <c r="CK15" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="CL15"/>
       <c r="CM15"/>
       <c r="CN15" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="CO15"/>
       <c r="CP15"/>
@@ -3237,12 +3237,12 @@
       <c r="CI16"/>
       <c r="CJ16"/>
       <c r="CK16" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="CL16"/>
       <c r="CM16"/>
       <c r="CN16" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="CO16"/>
       <c r="CP16"/>
@@ -3405,12 +3405,12 @@
       <c r="CI17"/>
       <c r="CJ17"/>
       <c r="CK17" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="CL17"/>
       <c r="CM17"/>
       <c r="CN17" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="CO17" t="n">
         <v>1</v>
@@ -3575,12 +3575,12 @@
       <c r="CI18"/>
       <c r="CJ18"/>
       <c r="CK18" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="CL18"/>
       <c r="CM18"/>
       <c r="CN18" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="CO18" t="n">
         <v>1</v>
@@ -3745,12 +3745,12 @@
       <c r="CI19"/>
       <c r="CJ19"/>
       <c r="CK19" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="CL19"/>
       <c r="CM19"/>
       <c r="CN19" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="CO19" t="n">
         <v>1</v>
@@ -3911,12 +3911,12 @@
       <c r="CI20"/>
       <c r="CJ20"/>
       <c r="CK20" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="CL20"/>
       <c r="CM20"/>
       <c r="CN20" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="CO20"/>
       <c r="CP20"/>
@@ -4075,12 +4075,12 @@
       <c r="CI21"/>
       <c r="CJ21"/>
       <c r="CK21" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="CL21"/>
       <c r="CM21"/>
       <c r="CN21" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="CO21"/>
       <c r="CP21"/>
@@ -4239,12 +4239,12 @@
       <c r="CI22"/>
       <c r="CJ22"/>
       <c r="CK22" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="CL22"/>
       <c r="CM22"/>
       <c r="CN22" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="CO22"/>
       <c r="CP22"/>
@@ -4407,12 +4407,12 @@
       <c r="CI23"/>
       <c r="CJ23"/>
       <c r="CK23" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="CL23"/>
       <c r="CM23"/>
       <c r="CN23" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="CO23" t="n">
         <v>1</v>
@@ -4577,12 +4577,12 @@
       <c r="CI24"/>
       <c r="CJ24"/>
       <c r="CK24" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="CL24"/>
       <c r="CM24"/>
       <c r="CN24" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="CO24" t="n">
         <v>1</v>
@@ -4747,12 +4747,12 @@
       <c r="CI25"/>
       <c r="CJ25"/>
       <c r="CK25" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="CL25"/>
       <c r="CM25"/>
       <c r="CN25" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="CO25" t="n">
         <v>1</v>
@@ -6635,12 +6635,12 @@
       <c r="CI38"/>
       <c r="CJ38"/>
       <c r="CK38" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="CL38"/>
       <c r="CM38"/>
       <c r="CN38" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="CO38"/>
       <c r="CP38"/>
@@ -6799,12 +6799,12 @@
       <c r="CI39"/>
       <c r="CJ39"/>
       <c r="CK39" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="CL39"/>
       <c r="CM39"/>
       <c r="CN39" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="CO39"/>
       <c r="CP39"/>
@@ -6963,12 +6963,12 @@
       <c r="CI40"/>
       <c r="CJ40"/>
       <c r="CK40" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="CL40"/>
       <c r="CM40"/>
       <c r="CN40" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="CO40"/>
       <c r="CP40"/>
@@ -7131,12 +7131,12 @@
       <c r="CI41"/>
       <c r="CJ41"/>
       <c r="CK41" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="CL41"/>
       <c r="CM41"/>
       <c r="CN41" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="CO41" t="n">
         <v>1</v>
@@ -7301,12 +7301,12 @@
       <c r="CI42"/>
       <c r="CJ42"/>
       <c r="CK42" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="CL42"/>
       <c r="CM42"/>
       <c r="CN42" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="CO42" t="n">
         <v>1</v>
@@ -7471,12 +7471,12 @@
       <c r="CI43"/>
       <c r="CJ43"/>
       <c r="CK43" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="CL43"/>
       <c r="CM43"/>
       <c r="CN43" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="CO43" t="n">
         <v>1</v>
@@ -7637,12 +7637,12 @@
       <c r="CI44"/>
       <c r="CJ44"/>
       <c r="CK44" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="CL44"/>
       <c r="CM44"/>
       <c r="CN44" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="CO44"/>
       <c r="CP44"/>
@@ -7801,12 +7801,12 @@
       <c r="CI45"/>
       <c r="CJ45"/>
       <c r="CK45" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="CL45"/>
       <c r="CM45"/>
       <c r="CN45" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="CO45"/>
       <c r="CP45"/>
@@ -7965,12 +7965,12 @@
       <c r="CI46"/>
       <c r="CJ46"/>
       <c r="CK46" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="CL46"/>
       <c r="CM46"/>
       <c r="CN46" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="CO46"/>
       <c r="CP46"/>
@@ -8133,12 +8133,12 @@
       <c r="CI47"/>
       <c r="CJ47"/>
       <c r="CK47" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="CL47"/>
       <c r="CM47"/>
       <c r="CN47" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="CO47" t="n">
         <v>1</v>
@@ -8303,12 +8303,12 @@
       <c r="CI48"/>
       <c r="CJ48"/>
       <c r="CK48" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="CL48"/>
       <c r="CM48"/>
       <c r="CN48" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="CO48" t="n">
         <v>1</v>
@@ -8473,12 +8473,12 @@
       <c r="CI49"/>
       <c r="CJ49"/>
       <c r="CK49" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="CL49"/>
       <c r="CM49"/>
       <c r="CN49" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="CO49" t="n">
         <v>1</v>
@@ -10388,7 +10388,7 @@
       <c r="CL62"/>
       <c r="CM62"/>
       <c r="CN62" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="CO62"/>
       <c r="CP62"/>
@@ -10556,7 +10556,7 @@
       <c r="CL63"/>
       <c r="CM63"/>
       <c r="CN63" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="CO63"/>
       <c r="CP63"/>
@@ -10724,7 +10724,7 @@
       <c r="CL64"/>
       <c r="CM64"/>
       <c r="CN64" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="CO64"/>
       <c r="CP64"/>
@@ -10891,12 +10891,12 @@
       <c r="CI65"/>
       <c r="CJ65"/>
       <c r="CK65" t="n">
-        <v>1.9</v>
+        <v>9.3</v>
       </c>
       <c r="CL65"/>
       <c r="CM65"/>
       <c r="CN65" t="n">
-        <v>39</v>
+        <v>32.7</v>
       </c>
       <c r="CO65" t="n">
         <v>1</v>
@@ -11065,12 +11065,12 @@
       <c r="CI66"/>
       <c r="CJ66"/>
       <c r="CK66" t="n">
-        <v>1.9</v>
+        <v>9.3</v>
       </c>
       <c r="CL66"/>
       <c r="CM66"/>
       <c r="CN66" t="n">
-        <v>39</v>
+        <v>32.7</v>
       </c>
       <c r="CO66" t="n">
         <v>1</v>
@@ -11239,12 +11239,12 @@
       <c r="CI67"/>
       <c r="CJ67"/>
       <c r="CK67" t="n">
-        <v>1.9</v>
+        <v>9.3</v>
       </c>
       <c r="CL67"/>
       <c r="CM67"/>
       <c r="CN67" t="n">
-        <v>39</v>
+        <v>32.7</v>
       </c>
       <c r="CO67" t="n">
         <v>1</v>
@@ -11409,12 +11409,12 @@
       <c r="CI68"/>
       <c r="CJ68"/>
       <c r="CK68" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="CL68"/>
       <c r="CM68"/>
       <c r="CN68" t="n">
-        <v>72</v>
+        <v>14.7</v>
       </c>
       <c r="CO68"/>
       <c r="CP68"/>
@@ -11577,12 +11577,12 @@
       <c r="CI69"/>
       <c r="CJ69"/>
       <c r="CK69" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="CL69"/>
       <c r="CM69"/>
       <c r="CN69" t="n">
-        <v>72</v>
+        <v>14.7</v>
       </c>
       <c r="CO69"/>
       <c r="CP69"/>
@@ -11745,12 +11745,12 @@
       <c r="CI70"/>
       <c r="CJ70"/>
       <c r="CK70" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="CL70"/>
       <c r="CM70"/>
       <c r="CN70" t="n">
-        <v>72</v>
+        <v>14.7</v>
       </c>
       <c r="CO70"/>
       <c r="CP70"/>
@@ -11917,12 +11917,12 @@
       <c r="CI71"/>
       <c r="CJ71"/>
       <c r="CK71" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="CL71"/>
       <c r="CM71"/>
       <c r="CN71" t="n">
-        <v>11.9</v>
+        <v>9</v>
       </c>
       <c r="CO71" t="n">
         <v>1</v>
@@ -12091,12 +12091,12 @@
       <c r="CI72"/>
       <c r="CJ72"/>
       <c r="CK72" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="CL72"/>
       <c r="CM72"/>
       <c r="CN72" t="n">
-        <v>11.9</v>
+        <v>9</v>
       </c>
       <c r="CO72" t="n">
         <v>1</v>
@@ -12265,12 +12265,12 @@
       <c r="CI73"/>
       <c r="CJ73"/>
       <c r="CK73" t="n">
-        <v>6.3</v>
+        <v>5.1</v>
       </c>
       <c r="CL73"/>
       <c r="CM73"/>
       <c r="CN73" t="n">
-        <v>11.9</v>
+        <v>9</v>
       </c>
       <c r="CO73" t="n">
         <v>1</v>
@@ -14199,12 +14199,12 @@
       <c r="CI86"/>
       <c r="CJ86"/>
       <c r="CK86" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="CL86"/>
       <c r="CM86"/>
       <c r="CN86" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="CO86"/>
       <c r="CP86" t="n">
@@ -14369,12 +14369,12 @@
       <c r="CI87"/>
       <c r="CJ87"/>
       <c r="CK87" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="CL87"/>
       <c r="CM87"/>
       <c r="CN87" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="CO87"/>
       <c r="CP87" t="n">
@@ -14539,12 +14539,12 @@
       <c r="CI88"/>
       <c r="CJ88"/>
       <c r="CK88" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="CL88"/>
       <c r="CM88"/>
       <c r="CN88" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="CO88"/>
       <c r="CP88" t="n">
@@ -14713,19 +14713,19 @@
       <c r="CI89"/>
       <c r="CJ89"/>
       <c r="CK89" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="CL89"/>
       <c r="CM89"/>
       <c r="CN89" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="CO89" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="CP89"/>
       <c r="CQ89" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="CR89"/>
       <c r="CS89"/>
@@ -14889,19 +14889,19 @@
       <c r="CI90"/>
       <c r="CJ90"/>
       <c r="CK90" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="CL90"/>
       <c r="CM90"/>
       <c r="CN90" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="CO90" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="CP90"/>
       <c r="CQ90" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="CR90"/>
       <c r="CS90"/>
@@ -15065,19 +15065,19 @@
       <c r="CI91"/>
       <c r="CJ91"/>
       <c r="CK91" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="CL91"/>
       <c r="CM91"/>
       <c r="CN91" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="CO91" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="CP91"/>
       <c r="CQ91" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="CR91"/>
       <c r="CS91"/>
@@ -15237,16 +15237,16 @@
       <c r="CI92"/>
       <c r="CJ92"/>
       <c r="CK92" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="CL92"/>
       <c r="CM92"/>
       <c r="CN92" t="n">
-        <v>8</v>
+        <v>15.4</v>
       </c>
       <c r="CO92"/>
       <c r="CP92" t="n">
-        <v>6.7</v>
+        <v>8.7</v>
       </c>
       <c r="CQ92"/>
       <c r="CR92"/>
@@ -15407,16 +15407,16 @@
       <c r="CI93"/>
       <c r="CJ93"/>
       <c r="CK93" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="CL93"/>
       <c r="CM93"/>
       <c r="CN93" t="n">
-        <v>8</v>
+        <v>15.4</v>
       </c>
       <c r="CO93"/>
       <c r="CP93" t="n">
-        <v>6.7</v>
+        <v>8.7</v>
       </c>
       <c r="CQ93"/>
       <c r="CR93"/>
@@ -15577,16 +15577,16 @@
       <c r="CI94"/>
       <c r="CJ94"/>
       <c r="CK94" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="CL94"/>
       <c r="CM94"/>
       <c r="CN94" t="n">
-        <v>8</v>
+        <v>15.4</v>
       </c>
       <c r="CO94"/>
       <c r="CP94" t="n">
-        <v>6.7</v>
+        <v>8.7</v>
       </c>
       <c r="CQ94"/>
       <c r="CR94"/>
@@ -15751,19 +15751,19 @@
       <c r="CI95"/>
       <c r="CJ95"/>
       <c r="CK95" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="CL95"/>
       <c r="CM95"/>
       <c r="CN95" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="CO95" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="CP95"/>
       <c r="CQ95" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="CR95"/>
       <c r="CS95"/>
@@ -15927,19 +15927,19 @@
       <c r="CI96"/>
       <c r="CJ96"/>
       <c r="CK96" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="CL96"/>
       <c r="CM96"/>
       <c r="CN96" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="CO96" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="CP96"/>
       <c r="CQ96" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="CR96"/>
       <c r="CS96"/>
@@ -16103,19 +16103,19 @@
       <c r="CI97"/>
       <c r="CJ97"/>
       <c r="CK97" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="CL97"/>
       <c r="CM97"/>
       <c r="CN97" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="CO97" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="CP97"/>
       <c r="CQ97" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="CR97"/>
       <c r="CS97"/>
@@ -18039,12 +18039,12 @@
       <c r="CI110"/>
       <c r="CJ110"/>
       <c r="CK110" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="CL110"/>
       <c r="CM110"/>
       <c r="CN110" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="CO110"/>
       <c r="CP110"/>
@@ -18209,12 +18209,12 @@
       <c r="CI111"/>
       <c r="CJ111"/>
       <c r="CK111" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="CL111"/>
       <c r="CM111"/>
       <c r="CN111" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="CO111"/>
       <c r="CP111"/>
@@ -18379,12 +18379,12 @@
       <c r="CI112"/>
       <c r="CJ112"/>
       <c r="CK112" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="CL112"/>
       <c r="CM112"/>
       <c r="CN112" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="CO112"/>
       <c r="CP112"/>
@@ -18553,12 +18553,12 @@
       <c r="CI113"/>
       <c r="CJ113"/>
       <c r="CK113" t="n">
-        <v>3634.1</v>
+        <v>3.2</v>
       </c>
       <c r="CL113"/>
       <c r="CM113"/>
       <c r="CN113" t="n">
-        <v>3634.9</v>
+        <v>3.2</v>
       </c>
       <c r="CO113" t="n">
         <v>1.1</v>
@@ -18566,7 +18566,7 @@
       <c r="CP113"/>
       <c r="CQ113"/>
       <c r="CR113" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="CS113"/>
       <c r="CT113"/>
@@ -18729,12 +18729,12 @@
       <c r="CI114"/>
       <c r="CJ114"/>
       <c r="CK114" t="n">
-        <v>3634.1</v>
+        <v>3.2</v>
       </c>
       <c r="CL114"/>
       <c r="CM114"/>
       <c r="CN114" t="n">
-        <v>3634.9</v>
+        <v>3.2</v>
       </c>
       <c r="CO114" t="n">
         <v>1.1</v>
@@ -18742,7 +18742,7 @@
       <c r="CP114"/>
       <c r="CQ114"/>
       <c r="CR114" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="CS114"/>
       <c r="CT114"/>
@@ -18905,12 +18905,12 @@
       <c r="CI115"/>
       <c r="CJ115"/>
       <c r="CK115" t="n">
-        <v>3634.1</v>
+        <v>3.2</v>
       </c>
       <c r="CL115"/>
       <c r="CM115"/>
       <c r="CN115" t="n">
-        <v>3634.9</v>
+        <v>3.2</v>
       </c>
       <c r="CO115" t="n">
         <v>1.1</v>
@@ -18918,7 +18918,7 @@
       <c r="CP115"/>
       <c r="CQ115"/>
       <c r="CR115" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="CS115"/>
       <c r="CT115"/>
@@ -19077,18 +19077,18 @@
       <c r="CI116"/>
       <c r="CJ116"/>
       <c r="CK116" t="n">
-        <v>1.8</v>
+        <v>12.6</v>
       </c>
       <c r="CL116"/>
       <c r="CM116"/>
       <c r="CN116" t="n">
-        <v>2</v>
+        <v>17.5</v>
       </c>
       <c r="CO116"/>
       <c r="CP116"/>
       <c r="CQ116"/>
       <c r="CR116" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="CS116"/>
       <c r="CT116"/>
@@ -19247,18 +19247,18 @@
       <c r="CI117"/>
       <c r="CJ117"/>
       <c r="CK117" t="n">
-        <v>1.8</v>
+        <v>12.6</v>
       </c>
       <c r="CL117"/>
       <c r="CM117"/>
       <c r="CN117" t="n">
-        <v>2</v>
+        <v>17.5</v>
       </c>
       <c r="CO117"/>
       <c r="CP117"/>
       <c r="CQ117"/>
       <c r="CR117" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="CS117"/>
       <c r="CT117"/>
@@ -19417,18 +19417,18 @@
       <c r="CI118"/>
       <c r="CJ118"/>
       <c r="CK118" t="n">
-        <v>1.8</v>
+        <v>12.6</v>
       </c>
       <c r="CL118"/>
       <c r="CM118"/>
       <c r="CN118" t="n">
-        <v>2</v>
+        <v>17.5</v>
       </c>
       <c r="CO118"/>
       <c r="CP118"/>
       <c r="CQ118"/>
       <c r="CR118" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="CS118"/>
       <c r="CT118"/>
@@ -19591,20 +19591,20 @@
       <c r="CI119"/>
       <c r="CJ119"/>
       <c r="CK119" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="CL119"/>
       <c r="CM119"/>
       <c r="CN119" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="CO119" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="CP119"/>
       <c r="CQ119"/>
       <c r="CR119" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="CS119"/>
       <c r="CT119"/>
@@ -19767,20 +19767,20 @@
       <c r="CI120"/>
       <c r="CJ120"/>
       <c r="CK120" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="CL120"/>
       <c r="CM120"/>
       <c r="CN120" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="CO120" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="CP120"/>
       <c r="CQ120"/>
       <c r="CR120" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="CS120"/>
       <c r="CT120"/>
@@ -19943,20 +19943,20 @@
       <c r="CI121"/>
       <c r="CJ121"/>
       <c r="CK121" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="CL121"/>
       <c r="CM121"/>
       <c r="CN121" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="CO121" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="CP121"/>
       <c r="CQ121"/>
       <c r="CR121" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="CS121"/>
       <c r="CT121"/>
@@ -21884,12 +21884,12 @@
       <c r="CL134"/>
       <c r="CM134"/>
       <c r="CN134" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="CO134"/>
       <c r="CP134"/>
       <c r="CQ134" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="CR134"/>
       <c r="CS134"/>
@@ -22054,12 +22054,12 @@
       <c r="CL135"/>
       <c r="CM135"/>
       <c r="CN135" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="CO135"/>
       <c r="CP135"/>
       <c r="CQ135" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="CR135"/>
       <c r="CS135"/>
@@ -22224,12 +22224,12 @@
       <c r="CL136"/>
       <c r="CM136"/>
       <c r="CN136" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="CO136"/>
       <c r="CP136"/>
       <c r="CQ136" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="CR136"/>
       <c r="CS136"/>
@@ -22393,18 +22393,18 @@
       <c r="CI137"/>
       <c r="CJ137"/>
       <c r="CK137" t="n">
-        <v>438.4</v>
+        <v>3.6</v>
       </c>
       <c r="CL137"/>
       <c r="CM137"/>
       <c r="CN137" t="n">
-        <v>373.6</v>
+        <v>4.3</v>
       </c>
       <c r="CO137" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="CP137" t="n">
-        <v>7.9</v>
+        <v>3.2</v>
       </c>
       <c r="CQ137"/>
       <c r="CR137"/>
@@ -22569,18 +22569,18 @@
       <c r="CI138"/>
       <c r="CJ138"/>
       <c r="CK138" t="n">
-        <v>438.4</v>
+        <v>3.6</v>
       </c>
       <c r="CL138"/>
       <c r="CM138"/>
       <c r="CN138" t="n">
-        <v>373.6</v>
+        <v>4.3</v>
       </c>
       <c r="CO138" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="CP138" t="n">
-        <v>7.9</v>
+        <v>3.2</v>
       </c>
       <c r="CQ138"/>
       <c r="CR138"/>
@@ -22745,18 +22745,18 @@
       <c r="CI139"/>
       <c r="CJ139"/>
       <c r="CK139" t="n">
-        <v>438.4</v>
+        <v>3.6</v>
       </c>
       <c r="CL139"/>
       <c r="CM139"/>
       <c r="CN139" t="n">
-        <v>373.6</v>
+        <v>4.3</v>
       </c>
       <c r="CO139" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="CP139" t="n">
-        <v>7.9</v>
+        <v>3.2</v>
       </c>
       <c r="CQ139"/>
       <c r="CR139"/>
@@ -23305,18 +23305,18 @@
       <c r="CI143"/>
       <c r="CJ143"/>
       <c r="CK143" t="n">
-        <v>7.9</v>
+        <v>2.1</v>
       </c>
       <c r="CL143"/>
       <c r="CM143"/>
       <c r="CN143" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="CO143" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="CP143" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="CQ143"/>
       <c r="CR143"/>
@@ -23481,18 +23481,18 @@
       <c r="CI144"/>
       <c r="CJ144"/>
       <c r="CK144" t="n">
-        <v>7.9</v>
+        <v>2.1</v>
       </c>
       <c r="CL144"/>
       <c r="CM144"/>
       <c r="CN144" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="CO144" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="CP144" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="CQ144"/>
       <c r="CR144"/>
@@ -23657,18 +23657,18 @@
       <c r="CI145"/>
       <c r="CJ145"/>
       <c r="CK145" t="n">
-        <v>7.9</v>
+        <v>2.1</v>
       </c>
       <c r="CL145"/>
       <c r="CM145"/>
       <c r="CN145" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="CO145" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="CP145" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="CQ145"/>
       <c r="CR145"/>
@@ -25489,21 +25489,21 @@
       <c r="CI158"/>
       <c r="CJ158"/>
       <c r="CK158" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="CL158"/>
       <c r="CM158"/>
       <c r="CN158" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="CO158"/>
       <c r="CP158" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="CQ158"/>
       <c r="CR158"/>
       <c r="CS158" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="CT158"/>
       <c r="CU158"/>
@@ -25665,21 +25665,21 @@
       <c r="CI159"/>
       <c r="CJ159"/>
       <c r="CK159" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="CL159"/>
       <c r="CM159"/>
       <c r="CN159" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="CO159"/>
       <c r="CP159" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="CQ159"/>
       <c r="CR159"/>
       <c r="CS159" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="CT159"/>
       <c r="CU159"/>
@@ -25841,21 +25841,21 @@
       <c r="CI160"/>
       <c r="CJ160"/>
       <c r="CK160" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="CL160"/>
       <c r="CM160"/>
       <c r="CN160" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="CO160"/>
       <c r="CP160" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="CQ160"/>
       <c r="CR160"/>
       <c r="CS160" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="CT160"/>
       <c r="CU160"/>
@@ -26785,21 +26785,21 @@
       <c r="CI167"/>
       <c r="CJ167"/>
       <c r="CK167" t="n">
-        <v>2.3</v>
+        <v>8.5</v>
       </c>
       <c r="CL167"/>
       <c r="CM167"/>
       <c r="CN167" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="CO167" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="CP167"/>
       <c r="CQ167"/>
       <c r="CR167"/>
       <c r="CS167" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="CT167"/>
       <c r="CU167"/>
@@ -26961,21 +26961,21 @@
       <c r="CI168"/>
       <c r="CJ168"/>
       <c r="CK168" t="n">
-        <v>2.3</v>
+        <v>8.5</v>
       </c>
       <c r="CL168"/>
       <c r="CM168"/>
       <c r="CN168" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="CO168" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="CP168"/>
       <c r="CQ168"/>
       <c r="CR168"/>
       <c r="CS168" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="CT168"/>
       <c r="CU168"/>
@@ -27137,21 +27137,21 @@
       <c r="CI169"/>
       <c r="CJ169"/>
       <c r="CK169" t="n">
-        <v>2.3</v>
+        <v>8.5</v>
       </c>
       <c r="CL169"/>
       <c r="CM169"/>
       <c r="CN169" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="CO169" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="CP169"/>
       <c r="CQ169"/>
       <c r="CR169"/>
       <c r="CS169" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="CT169"/>
       <c r="CU169"/>
@@ -28969,12 +28969,12 @@
       <c r="CI182"/>
       <c r="CJ182"/>
       <c r="CK182" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="CL182"/>
       <c r="CM182"/>
       <c r="CN182" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="CO182"/>
       <c r="CP182"/>
@@ -28983,7 +28983,7 @@
         <v>1</v>
       </c>
       <c r="CS182" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="CT182"/>
       <c r="CU182"/>
@@ -29145,12 +29145,12 @@
       <c r="CI183"/>
       <c r="CJ183"/>
       <c r="CK183" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="CL183"/>
       <c r="CM183"/>
       <c r="CN183" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="CO183"/>
       <c r="CP183"/>
@@ -29159,7 +29159,7 @@
         <v>1</v>
       </c>
       <c r="CS183" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="CT183"/>
       <c r="CU183"/>
@@ -29321,12 +29321,12 @@
       <c r="CI184"/>
       <c r="CJ184"/>
       <c r="CK184" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="CL184"/>
       <c r="CM184"/>
       <c r="CN184" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="CO184"/>
       <c r="CP184"/>
@@ -29335,7 +29335,7 @@
         <v>1</v>
       </c>
       <c r="CS184" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="CT184"/>
       <c r="CU184"/>
@@ -30265,21 +30265,21 @@
       <c r="CI191"/>
       <c r="CJ191"/>
       <c r="CK191" t="n">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="CL191"/>
       <c r="CM191"/>
       <c r="CN191" t="n">
-        <v>9.1</v>
+        <v>2.5</v>
       </c>
       <c r="CO191" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="CP191"/>
       <c r="CQ191"/>
       <c r="CR191"/>
       <c r="CS191" t="n">
-        <v>10.1</v>
+        <v>4.4</v>
       </c>
       <c r="CT191"/>
       <c r="CU191"/>
@@ -30441,21 +30441,21 @@
       <c r="CI192"/>
       <c r="CJ192"/>
       <c r="CK192" t="n">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="CL192"/>
       <c r="CM192"/>
       <c r="CN192" t="n">
-        <v>9.1</v>
+        <v>2.5</v>
       </c>
       <c r="CO192" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="CP192"/>
       <c r="CQ192"/>
       <c r="CR192"/>
       <c r="CS192" t="n">
-        <v>10.1</v>
+        <v>4.4</v>
       </c>
       <c r="CT192"/>
       <c r="CU192"/>
@@ -30617,21 +30617,21 @@
       <c r="CI193"/>
       <c r="CJ193"/>
       <c r="CK193" t="n">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="CL193"/>
       <c r="CM193"/>
       <c r="CN193" t="n">
-        <v>9.1</v>
+        <v>2.5</v>
       </c>
       <c r="CO193" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="CP193"/>
       <c r="CQ193"/>
       <c r="CR193"/>
       <c r="CS193" t="n">
-        <v>10.1</v>
+        <v>4.4</v>
       </c>
       <c r="CT193"/>
       <c r="CU193"/>
@@ -32449,12 +32449,12 @@
       <c r="CI206"/>
       <c r="CJ206"/>
       <c r="CK206" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="CL206"/>
       <c r="CM206"/>
       <c r="CN206" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="CO206"/>
       <c r="CP206"/>
@@ -32463,7 +32463,7 @@
       </c>
       <c r="CR206"/>
       <c r="CS206" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="CT206"/>
       <c r="CU206"/>
@@ -32625,12 +32625,12 @@
       <c r="CI207"/>
       <c r="CJ207"/>
       <c r="CK207" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="CL207"/>
       <c r="CM207"/>
       <c r="CN207" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="CO207"/>
       <c r="CP207"/>
@@ -32639,7 +32639,7 @@
       </c>
       <c r="CR207"/>
       <c r="CS207" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="CT207"/>
       <c r="CU207"/>
@@ -32801,12 +32801,12 @@
       <c r="CI208"/>
       <c r="CJ208"/>
       <c r="CK208" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="CL208"/>
       <c r="CM208"/>
       <c r="CN208" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="CO208"/>
       <c r="CP208"/>
@@ -32815,7 +32815,7 @@
       </c>
       <c r="CR208"/>
       <c r="CS208" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="CT208"/>
       <c r="CU208"/>
@@ -33745,21 +33745,21 @@
       <c r="CI215"/>
       <c r="CJ215"/>
       <c r="CK215" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="CL215"/>
       <c r="CM215"/>
       <c r="CN215" t="n">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="CO215" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="CP215"/>
       <c r="CQ215"/>
       <c r="CR215"/>
       <c r="CS215" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="CT215"/>
       <c r="CU215"/>
@@ -33921,21 +33921,21 @@
       <c r="CI216"/>
       <c r="CJ216"/>
       <c r="CK216" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="CL216"/>
       <c r="CM216"/>
       <c r="CN216" t="n">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="CO216" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="CP216"/>
       <c r="CQ216"/>
       <c r="CR216"/>
       <c r="CS216" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="CT216"/>
       <c r="CU216"/>
@@ -34097,21 +34097,21 @@
       <c r="CI217"/>
       <c r="CJ217"/>
       <c r="CK217" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="CL217"/>
       <c r="CM217"/>
       <c r="CN217" t="n">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="CO217" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="CP217"/>
       <c r="CQ217"/>
       <c r="CR217"/>
       <c r="CS217" t="n">
-        <v>4.2</v>
+        <v>7.5</v>
       </c>
       <c r="CT217"/>
       <c r="CU217"/>
